--- a/EMPTY VERSION ANSWERS.xlsx
+++ b/EMPTY VERSION ANSWERS.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="47">
   <si>
     <t>P01</t>
   </si>
@@ -151,6 +151,15 @@
   </si>
   <si>
     <t>Electrical and Electronics Engineering</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Female</t>
   </si>
 </sst>
 </file>
@@ -226,19 +235,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <font>
         <b val="0"/>
@@ -373,24 +370,12 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
         <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
       </font>
       <fill>
-        <patternFill patternType="none">
+        <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -412,6 +397,54 @@
         <scheme val="minor"/>
       </font>
       <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor auto="1"/>
@@ -471,10 +504,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Form Yanıtları 1-style" pivot="0" count="4">
-      <tableStyleElement type="wholeTable" size="0" dxfId="20"/>
-      <tableStyleElement type="headerRow" dxfId="19"/>
-      <tableStyleElement type="firstRowStripe" dxfId="18"/>
-      <tableStyleElement type="secondRowStripe" dxfId="17"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="21"/>
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="firstRowStripe" dxfId="19"/>
+      <tableStyleElement type="secondRowStripe" dxfId="18"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -489,24 +522,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:P21" dataDxfId="16">
-  <tableColumns count="16">
-    <tableColumn id="3" name="Participant  " dataDxfId="15"/>
-    <tableColumn id="4" name="Age " dataDxfId="14"/>
-    <tableColumn id="5" name="Department" dataDxfId="1"/>
-    <tableColumn id="8" name="Which hand is your dominant hand?" dataDxfId="0"/>
-    <tableColumn id="9" name="This image is visually appealing." dataDxfId="13"/>
-    <tableColumn id="10" name="I find the space in this image aesthetically beautiful" dataDxfId="12"/>
-    <tableColumn id="11" name="  I would find it pleasant to be in this space.  " dataDxfId="11"/>
-    <tableColumn id="12" name="This image is visually appealing.2" dataDxfId="10"/>
-    <tableColumn id="13" name="I find the space in this image aesthetically beautiful3" dataDxfId="9"/>
-    <tableColumn id="14" name="  I would find it pleasant to be in this space.  4" dataDxfId="8"/>
-    <tableColumn id="15" name="This image is visually appealing.3" dataDxfId="7"/>
-    <tableColumn id="16" name="I find the space in this image aesthetically beautiful4" dataDxfId="6"/>
-    <tableColumn id="17" name="  I would find it pleasant to be in this space.  5" dataDxfId="5"/>
-    <tableColumn id="18" name="This image is visually appealing.4" dataDxfId="4"/>
-    <tableColumn id="19" name="I find the space in this image aesthetically beautiful5" dataDxfId="3"/>
-    <tableColumn id="20" name="  I would find it pleasant to be in this space.  6" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:Q21" dataDxfId="17">
+  <tableColumns count="17">
+    <tableColumn id="3" name="Participant  " dataDxfId="16"/>
+    <tableColumn id="4" name="Age " dataDxfId="15"/>
+    <tableColumn id="2" name="Gender" dataDxfId="0"/>
+    <tableColumn id="5" name="Department" dataDxfId="14"/>
+    <tableColumn id="8" name="Which hand is your dominant hand?" dataDxfId="13"/>
+    <tableColumn id="9" name="This image is visually appealing." dataDxfId="12"/>
+    <tableColumn id="10" name="I find the space in this image aesthetically beautiful" dataDxfId="11"/>
+    <tableColumn id="11" name="  I would find it pleasant to be in this space.  " dataDxfId="10"/>
+    <tableColumn id="12" name="This image is visually appealing.2" dataDxfId="9"/>
+    <tableColumn id="13" name="I find the space in this image aesthetically beautiful3" dataDxfId="8"/>
+    <tableColumn id="14" name="  I would find it pleasant to be in this space.  4" dataDxfId="7"/>
+    <tableColumn id="15" name="This image is visually appealing.3" dataDxfId="6"/>
+    <tableColumn id="16" name="I find the space in this image aesthetically beautiful4" dataDxfId="5"/>
+    <tableColumn id="17" name="  I would find it pleasant to be in this space.  5" dataDxfId="4"/>
+    <tableColumn id="18" name="This image is visually appealing.4" dataDxfId="3"/>
+    <tableColumn id="19" name="I find the space in this image aesthetically beautiful5" dataDxfId="2"/>
+    <tableColumn id="20" name="  I would find it pleasant to be in this space.  6" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -713,29 +747,29 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" customWidth="1"/>
-    <col min="4" max="4" width="33.5546875" customWidth="1"/>
-    <col min="5" max="5" width="33.33203125" customWidth="1"/>
-    <col min="6" max="6" width="53.77734375" customWidth="1"/>
-    <col min="7" max="7" width="39.109375" customWidth="1"/>
-    <col min="8" max="8" width="32.21875" customWidth="1"/>
-    <col min="9" max="9" width="59.6640625" customWidth="1"/>
-    <col min="10" max="10" width="39.88671875" customWidth="1"/>
-    <col min="11" max="11" width="32.44140625" customWidth="1"/>
-    <col min="12" max="12" width="53.21875" customWidth="1"/>
-    <col min="13" max="13" width="34.6640625" customWidth="1"/>
-    <col min="14" max="14" width="28.44140625" customWidth="1"/>
-    <col min="15" max="15" width="37.6640625" customWidth="1"/>
-    <col min="16" max="16" width="34.6640625" customWidth="1"/>
-    <col min="17" max="22" width="18.88671875" customWidth="1"/>
+    <col min="2" max="3" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="36.21875" customWidth="1"/>
+    <col min="5" max="5" width="33.5546875" customWidth="1"/>
+    <col min="6" max="6" width="33.33203125" customWidth="1"/>
+    <col min="7" max="7" width="53.77734375" customWidth="1"/>
+    <col min="8" max="8" width="39.109375" customWidth="1"/>
+    <col min="9" max="9" width="32.21875" customWidth="1"/>
+    <col min="10" max="10" width="59.6640625" customWidth="1"/>
+    <col min="11" max="11" width="39.88671875" customWidth="1"/>
+    <col min="12" max="12" width="32.44140625" customWidth="1"/>
+    <col min="13" max="13" width="53.21875" customWidth="1"/>
+    <col min="14" max="14" width="34.6640625" customWidth="1"/>
+    <col min="15" max="15" width="28.44140625" customWidth="1"/>
+    <col min="16" max="16" width="37.6640625" customWidth="1"/>
+    <col min="17" max="17" width="34.6640625" customWidth="1"/>
+    <col min="18" max="23" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -743,81 +777,84 @@
         <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3">
         <v>19</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="3">
-        <v>4</v>
-      </c>
       <c r="F2" s="3">
         <v>4</v>
       </c>
       <c r="G2" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3">
         <v>4</v>
       </c>
       <c r="J2" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L2" s="3">
         <v>5</v>
@@ -826,16 +863,19 @@
         <v>5</v>
       </c>
       <c r="N2" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O2" s="3">
         <v>3</v>
       </c>
       <c r="P2" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -843,14 +883,14 @@
         <v>20</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="3">
-        <v>5</v>
-      </c>
       <c r="F3" s="3">
         <v>5</v>
       </c>
@@ -858,10 +898,10 @@
         <v>5</v>
       </c>
       <c r="H3" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" s="3">
         <v>5</v>
@@ -876,16 +916,19 @@
         <v>5</v>
       </c>
       <c r="N3" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O3" s="3">
         <v>4</v>
       </c>
       <c r="P3" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -893,14 +936,14 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="3">
-        <v>4</v>
-      </c>
       <c r="F4" s="3">
         <v>4</v>
       </c>
@@ -911,7 +954,7 @@
         <v>4</v>
       </c>
       <c r="I4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" s="3">
         <v>5</v>
@@ -926,16 +969,19 @@
         <v>5</v>
       </c>
       <c r="N4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P4" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -943,16 +989,16 @@
         <v>41</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="3">
-        <v>4</v>
-      </c>
       <c r="F5" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="3">
         <v>5</v>
@@ -976,16 +1022,19 @@
         <v>5</v>
       </c>
       <c r="N5" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P5" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q5" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -993,19 +1042,19 @@
         <v>19</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="3">
-        <v>4</v>
-      </c>
       <c r="F6" s="3">
         <v>4</v>
       </c>
       <c r="G6" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" s="3">
         <v>5</v>
@@ -1026,16 +1075,19 @@
         <v>5</v>
       </c>
       <c r="N6" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O6" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -1043,14 +1095,14 @@
         <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="3">
-        <v>5</v>
-      </c>
       <c r="F7" s="3">
         <v>5</v>
       </c>
@@ -1061,13 +1113,13 @@
         <v>5</v>
       </c>
       <c r="I7" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" s="3">
         <v>4</v>
       </c>
       <c r="K7" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7" s="3">
         <v>5</v>
@@ -1084,8 +1136,11 @@
       <c r="P7" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q7" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -1093,49 +1148,52 @@
         <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2</v>
       </c>
-      <c r="F8" s="3">
-        <v>3</v>
-      </c>
       <c r="G8" s="3">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>2</v>
       </c>
-      <c r="H8" s="3">
-        <v>3</v>
-      </c>
       <c r="I8" s="3">
         <v>3</v>
       </c>
       <c r="J8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>2</v>
       </c>
       <c r="L8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>2</v>
       </c>
       <c r="O8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -1143,19 +1201,19 @@
         <v>21</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="3">
-        <v>4</v>
-      </c>
       <c r="F9" s="3">
         <v>4</v>
       </c>
       <c r="G9" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H9" s="3">
         <v>5</v>
@@ -1167,25 +1225,28 @@
         <v>5</v>
       </c>
       <c r="K9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" s="3">
         <v>4</v>
       </c>
       <c r="M9" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O9" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P9" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -1193,31 +1254,31 @@
         <v>19</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="3">
-        <v>4</v>
-      </c>
       <c r="F10" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <v>4</v>
       </c>
       <c r="I10" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10" s="3">
         <v>5</v>
@@ -1226,16 +1287,19 @@
         <v>5</v>
       </c>
       <c r="N10" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10" s="3">
         <v>4</v>
       </c>
       <c r="P10" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1243,40 +1307,40 @@
         <v>18</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="3">
-        <v>4</v>
-      </c>
       <c r="F11" s="3">
         <v>4</v>
       </c>
       <c r="G11" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="3">
         <v>2</v>
       </c>
       <c r="J11" s="3">
+        <v>2</v>
+      </c>
+      <c r="K11" s="3">
         <v>1</v>
       </c>
-      <c r="K11" s="3">
-        <v>5</v>
-      </c>
       <c r="L11" s="3">
         <v>5</v>
       </c>
       <c r="M11" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O11" s="3">
         <v>2</v>
@@ -1284,8 +1348,11 @@
       <c r="P11" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q11" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1293,14 +1360,14 @@
         <v>26</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="3">
-        <v>4</v>
-      </c>
       <c r="F12" s="3">
         <v>4</v>
       </c>
@@ -1308,7 +1375,7 @@
         <v>4</v>
       </c>
       <c r="H12" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="3">
         <v>3</v>
@@ -1317,7 +1384,7 @@
         <v>3</v>
       </c>
       <c r="K12" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L12" s="3">
         <v>5</v>
@@ -1326,7 +1393,7 @@
         <v>5</v>
       </c>
       <c r="N12" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O12" s="3">
         <v>3</v>
@@ -1334,8 +1401,11 @@
       <c r="P12" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q12" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1343,19 +1413,19 @@
         <v>27</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="3">
-        <v>4</v>
-      </c>
       <c r="F13" s="3">
         <v>4</v>
       </c>
       <c r="G13" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H13" s="3">
         <v>5</v>
@@ -1384,8 +1454,11 @@
       <c r="P13" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q13" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -1393,49 +1466,52 @@
         <v>19</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="3">
-        <v>4</v>
-      </c>
       <c r="F14" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>5</v>
       </c>
       <c r="J14" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>5</v>
       </c>
       <c r="M14" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O14" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P14" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
@@ -1443,19 +1519,19 @@
         <v>24</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="3">
-        <v>4</v>
-      </c>
       <c r="F15" s="3">
         <v>4</v>
       </c>
       <c r="G15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="3">
         <v>5</v>
@@ -1476,7 +1552,7 @@
         <v>5</v>
       </c>
       <c r="N15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O15" s="3">
         <v>4</v>
@@ -1484,8 +1560,11 @@
       <c r="P15" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q15" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -1493,14 +1572,14 @@
         <v>21</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="3">
-        <v>5</v>
-      </c>
       <c r="F16" s="3">
         <v>5</v>
       </c>
@@ -1534,8 +1613,11 @@
       <c r="P16" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q16" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
@@ -1543,19 +1625,19 @@
         <v>21</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="3">
-        <v>4</v>
-      </c>
       <c r="F17" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="3">
         <v>4</v>
@@ -1570,13 +1652,13 @@
         <v>4</v>
       </c>
       <c r="L17" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17" s="3">
         <v>5</v>
       </c>
       <c r="N17" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O17" s="3">
         <v>4</v>
@@ -1584,8 +1666,11 @@
       <c r="P17" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q17" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
@@ -1593,14 +1678,14 @@
         <v>24</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="3">
-        <v>5</v>
-      </c>
       <c r="F18" s="3">
         <v>5</v>
       </c>
@@ -1608,7 +1693,7 @@
         <v>5</v>
       </c>
       <c r="H18" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" s="3">
         <v>4</v>
@@ -1617,7 +1702,7 @@
         <v>4</v>
       </c>
       <c r="K18" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L18" s="3">
         <v>5</v>
@@ -1626,7 +1711,7 @@
         <v>5</v>
       </c>
       <c r="N18" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18" s="3">
         <v>4</v>
@@ -1634,8 +1719,11 @@
       <c r="P18" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q18" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
@@ -1643,14 +1731,14 @@
         <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="3">
-        <v>5</v>
-      </c>
       <c r="F19" s="3">
         <v>5</v>
       </c>
@@ -1684,8 +1772,11 @@
       <c r="P19" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q19" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
@@ -1693,31 +1784,31 @@
         <v>18</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="3">
-        <v>5</v>
-      </c>
       <c r="F20" s="3">
         <v>5</v>
       </c>
       <c r="G20" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" s="3">
         <v>5</v>
       </c>
       <c r="J20" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K20" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L20" s="3">
         <v>5</v>
@@ -1726,16 +1817,19 @@
         <v>5</v>
       </c>
       <c r="N20" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O20" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P20" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
@@ -1743,19 +1837,19 @@
         <v>20</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="3">
-        <v>4</v>
-      </c>
       <c r="F21" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21" s="3">
         <v>4</v>
@@ -1767,7 +1861,7 @@
         <v>4</v>
       </c>
       <c r="K21" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L21" s="3">
         <v>5</v>
@@ -1776,12 +1870,15 @@
         <v>5</v>
       </c>
       <c r="N21" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O21" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P21" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>3</v>
       </c>
     </row>
